--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N92_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N92_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.02018130865535</v>
+        <v>1.790779462656494</v>
       </c>
       <c r="D2" t="n">
-        <v>3.941211521640483</v>
+        <v>0.6404468722665785</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F2" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.772772874802806</v>
+        <v>1.100575592155456</v>
       </c>
       <c r="D3" t="n">
-        <v>6.796411839264064</v>
+        <v>1.10441692388041</v>
       </c>
       <c r="E3" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F3" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.14517094916582</v>
+        <v>6.361090279239447</v>
       </c>
       <c r="D4" t="n">
-        <v>39.25187846469673</v>
+        <v>6.378430250513219</v>
       </c>
       <c r="E4" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F4" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.21362558073993</v>
+        <v>4.90971415687024</v>
       </c>
       <c r="D5" t="n">
-        <v>30.69369080497904</v>
+        <v>4.987724755809094</v>
       </c>
       <c r="E5" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F5" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.49277488631352</v>
+        <v>4.630075919025947</v>
       </c>
       <c r="D6" t="n">
-        <v>28.23232140627897</v>
+        <v>4.587752228520333</v>
       </c>
       <c r="E6" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F6" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.80746267232046</v>
+        <v>6.143712684252075</v>
       </c>
       <c r="D7" t="n">
-        <v>38.10988960908448</v>
+        <v>6.192857061476229</v>
       </c>
       <c r="E7" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F7" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.39699365658231</v>
+        <v>6.402011469194625</v>
       </c>
       <c r="D8" t="n">
-        <v>38.89439355632688</v>
+        <v>6.320338952903119</v>
       </c>
       <c r="E8" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F8" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.0504250075243</v>
+        <v>3.258194063722698</v>
       </c>
       <c r="D9" t="n">
-        <v>19.73528523261272</v>
+        <v>3.206983850299568</v>
       </c>
       <c r="E9" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F9" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.97701309273267</v>
+        <v>5.358764627569059</v>
       </c>
       <c r="D10" t="n">
-        <v>32.46335065198641</v>
+        <v>5.275294480947792</v>
       </c>
       <c r="E10" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F10" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.86434996795173</v>
+        <v>5.990456869792157</v>
       </c>
       <c r="D11" t="n">
-        <v>36.56786052750363</v>
+        <v>5.942277335719339</v>
       </c>
       <c r="E11" t="n">
-        <v>11.2255820503982</v>
+        <v>1.824157083189707</v>
       </c>
       <c r="F11" t="n">
-        <v>12.41789652425021</v>
+        <v>2.017908185190659</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
